--- a/data.xlsx
+++ b/data.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A31392-8F62-4165-94A2-08342716E013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9DFCE8-CD23-4EE8-A323-A81AA2F8F19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2663" yWindow="2798" windowWidth="17549" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="5603" windowWidth="17550" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="持仓数据" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>名称</t>
   </si>
@@ -28,55 +41,41 @@
     <t>代码</t>
   </si>
   <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>收盘</t>
-  </si>
-  <si>
-    <t>入场价</t>
-  </si>
-  <si>
-    <t>入场涨跌幅</t>
-  </si>
-  <si>
-    <t>垂仓价</t>
-  </si>
-  <si>
-    <t>垂仓涨跌幅</t>
-  </si>
-  <si>
-    <t>今日涨跌幅</t>
-  </si>
-  <si>
-    <t>昨日涨跌幅</t>
-  </si>
-  <si>
-    <t>止盈1价</t>
-  </si>
-  <si>
-    <t>止盈1涨跌幅</t>
-  </si>
-  <si>
-    <t>止盈2价</t>
-  </si>
-  <si>
-    <t>年初价</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
     <t>齐翔腾达</t>
   </si>
   <si>
     <t>002408</t>
   </si>
   <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>齐翔腾达2</t>
+    <t>钢研高纳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重仓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/5/10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -84,7 +83,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +103,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,9 +132,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -431,80 +445,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" style="3" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
@@ -516,73 +505,31 @@
       <c r="G2">
         <v>4.5</v>
       </c>
-      <c r="H2">
-        <v>32.89</v>
-      </c>
-      <c r="I2">
-        <v>-1.81</v>
-      </c>
-      <c r="J2">
-        <v>0.16</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-      <c r="L2">
-        <v>67.2</v>
-      </c>
-      <c r="M2">
-        <v>15</v>
-      </c>
-      <c r="N2">
-        <v>4.87</v>
-      </c>
-      <c r="O2" t="s">
-        <v>17</v>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>2409</v>
-      </c>
-      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>300034</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>5.5</v>
-      </c>
       <c r="F3">
-        <v>8.73</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
-      </c>
-      <c r="H3">
-        <v>32.89</v>
-      </c>
-      <c r="I3">
-        <v>-1.81</v>
-      </c>
-      <c r="J3">
-        <v>0.16</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>67.2</v>
-      </c>
-      <c r="M3">
-        <v>15</v>
-      </c>
-      <c r="N3">
-        <v>4.87</v>
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\股票研究\00 watch\myGoal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9DFCE8-CD23-4EE8-A323-A81AA2F8F19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBD6398-275F-4709-AC87-FA8E25E183AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="5603" windowWidth="17550" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5573" yWindow="2700" windowWidth="17549" windowHeight="10883" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="持仓数据" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
   <si>
     <t>名称</t>
   </si>
@@ -47,10 +47,6 @@
     <t>002408</t>
   </si>
   <si>
-    <t>钢研高纳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -67,15 +63,183 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>备注2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数据时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026/5/10</t>
+    <t>化工</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中化国际</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国泰集团</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>民爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/5/11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中钢国际</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000928</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海南橡胶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>601118</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农林牧渔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>易普力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002096</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯龙股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002783</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪峰科技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>603227</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星湖科技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600866</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>北元集团</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>601568</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>化工PVC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>岳阳兴长</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000819</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>止盈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天康生物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国中冶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>601618</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>安纳达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002136</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛋氨酸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川美丰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000731</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>尿素</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中牧股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600195</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双环科技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000707</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯碱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东海化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>000822</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中盐化工</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600328</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -132,17 +296,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -445,91 +610,424 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10" style="6" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>5.5</v>
       </c>
       <c r="F2">
-        <v>8.73</v>
-      </c>
-      <c r="G2">
-        <v>4.5</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6">
+        <v>600500</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>4.2</v>
+      </c>
+      <c r="E3">
         <v>4</v>
       </c>
-      <c r="B3" s="3">
-        <v>300034</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6">
+        <v>603977</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>13.5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>6.6</v>
+      </c>
+      <c r="E5">
+        <v>6.5</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E9">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>5.7</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>11</v>
+      <c r="E14">
+        <v>2.95</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>6.5</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <v>7.4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>5.85</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19">
+        <v>5.3</v>
+      </c>
+      <c r="E19">
+        <v>4.8</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>7.3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\股票研究\00 watch\myGoal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBD6398-275F-4709-AC87-FA8E25E183AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED68BEDA-FA78-4D4C-99A1-4007C3BE994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5573" yWindow="2700" windowWidth="17549" windowHeight="10883" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4268" yWindow="3278" windowWidth="17550" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="持仓数据" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
     <t>名称</t>
   </si>
@@ -48,199 +48,181 @@
   </si>
   <si>
     <t>分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>入场</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>重仓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>止盈</t>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>数据时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>化工</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/5/11</t>
   </si>
   <si>
     <t>中化国际</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600500</t>
   </si>
   <si>
     <t>国泰集团</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>603977</t>
   </si>
   <si>
     <t>民爆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/5/11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中钢国际</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000928</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工程</t>
   </si>
   <si>
     <t>海南橡胶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>601118</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>农林牧渔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>易普力</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>002096</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>凯龙股份</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>002783</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>雪峰科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>603227</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>星湖科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>600866</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>北元集团</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>601568</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>化工PVC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（26.5.13）鱼大回复可以重仓的位置，今天价格3.87</t>
   </si>
   <si>
     <t>岳阳兴长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000819</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>止盈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>天康生物</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>002100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（26.5.13）有人提问：7.51的成本，是不是高了点
+鱼大回复：跌多了就再买点，当天价格7.3</t>
   </si>
   <si>
     <t>中国中冶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>601618</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>工程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>安纳达</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>002136</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>蛋氨酸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>四川美丰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000731</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>尿素</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中牧股份</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>600195</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（26.5.13）当天7.27，鱼大回复可以入手</t>
   </si>
   <si>
     <t>双环科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000707</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>纯碱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>山东海化</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>000822</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中盐化工</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>600328</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恒邦股份</t>
+  </si>
+  <si>
+    <t>002237</t>
+  </si>
+  <si>
+    <t>有色</t>
+  </si>
+  <si>
+    <t>（26.5.19）鱼大pyq，13~14就是好价格</t>
+  </si>
+  <si>
+    <t>2026/5/19</t>
   </si>
 </sst>
 </file>
@@ -256,12 +238,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -271,9 +247,19 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -296,18 +282,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -323,6 +339,59 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9511DC3-0A2A-BDE9-40F0-596951FDFDF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5857875" y="2228850"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -610,428 +679,500 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" customWidth="1"/>
-    <col min="3" max="4" width="8" customWidth="1"/>
+    <col min="2" max="2" width="10" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" style="16" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="12" style="3" customWidth="1"/>
+    <col min="7" max="7" width="55.9296875" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="15">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="F2" s="9">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="E3" s="9">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9">
+        <v>7</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="15">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="15">
+        <v>6.6</v>
+      </c>
+      <c r="E5" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="15">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="15">
+        <v>11</v>
+      </c>
+      <c r="E7" s="9">
+        <v>11</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="15">
+        <v>9</v>
+      </c>
+      <c r="E8" s="9">
+        <v>8.75</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="15">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E9" s="9">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="15">
+        <v>6</v>
+      </c>
+      <c r="E10" s="9">
+        <v>5.7</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="15">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="15">
+        <v>14</v>
+      </c>
+      <c r="E12" s="9">
+        <v>12</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="15">
+        <v>7.3</v>
+      </c>
+      <c r="E13" s="9">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="F13" s="12"/>
+      <c r="G13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="15">
+        <v>12</v>
+      </c>
+      <c r="E15" s="9">
+        <v>10</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="15">
+        <v>7</v>
+      </c>
+      <c r="E16" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="15">
+        <v>7.3</v>
+      </c>
+      <c r="E17" s="9">
+        <v>7</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="15">
+        <v>6</v>
+      </c>
+      <c r="E18" s="9">
+        <v>5.85</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="E19" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>5.5</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="E20" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="15">
+        <v>14</v>
+      </c>
+      <c r="E21" s="9">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6">
-        <v>600500</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>4.2</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6">
-        <v>603977</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>13.5</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5">
-        <v>6.6</v>
-      </c>
-      <c r="E5">
-        <v>6.5</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5.5</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>9</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E9">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>5.7</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>3.5</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>14</v>
-      </c>
-      <c r="E12">
-        <v>12</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13">
-        <v>7</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <v>2.95</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15">
-        <v>12</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16">
-        <v>7</v>
-      </c>
-      <c r="E16">
-        <v>6.5</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
-        <v>7.4</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>5.85</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19">
-        <v>5.3</v>
-      </c>
-      <c r="E19">
-        <v>4.8</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>7.3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>13</v>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>